--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -798,17 +798,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>The button is not working</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>KO</t>
+          <t>Next page button works correctly.</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link</t>
+          <t>Fixed: removed products?.meta.page and products?.meta.limit from useEffect deps. These caused the effect to re-run on page change and reset to page 1 via the debounced setTimeout. Now uses useRef to track current page for the auto-refresh interval.</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Blocked by PRO008</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>BL</t>
+          <t>Previous page button works correctly.</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link</t>
+          <t>Fixed as part of PRO008: same root cause resolved.</t>
         </is>
       </c>
     </row>

--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -798,17 +798,17 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Next page button works correctly.</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>FIXED</t>
+          <t>The button is not working</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>KO</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Fixed: removed products?.meta.page and products?.meta.limit from useEffect deps. These caused the effect to re-run on page change and reset to page 1 via the debounced setTimeout. Now uses useRef to track current page for the auto-refresh interval.</t>
+          <t>https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Previous page button works correctly.</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>FIXED</t>
+          <t>Blocked by PRO008</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>BL</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Fixed as part of PRO008: same root cause resolved.</t>
+          <t>https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link</t>
         </is>
       </c>
     </row>

--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB44CEC-93D5-4C91-BA9E-BA5CD0B0BC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F1817-93A8-4769-8538-8C2629ECADD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
   <si>
     <t>Num</t>
   </si>
@@ -122,25 +121,16 @@
     <t>Cancel creation</t>
   </si>
   <si>
-    <t>1. The user clicks Product home</t>
-  </si>
-  <si>
     <t>1. The user clicks icon pencil</t>
   </si>
   <si>
     <t>1. The user clicks icon garbage</t>
   </si>
   <si>
-    <t>1. The user clicks in a product</t>
-  </si>
-  <si>
     <t>1. The user chooses a categorie</t>
   </si>
   <si>
     <t>1. The user searches a product</t>
-  </si>
-  <si>
-    <t>1. The user clicks icon next page</t>
   </si>
   <si>
     <t>1. The user clicks icon previous page</t>
@@ -183,11 +173,6 @@
     <t>1. Previous next are displayed.</t>
   </si>
   <si>
-    <t>1. The user clicks "Nuevo producto"
-2. The user fills the fields.
-3. The user clicks "Crear"</t>
-  </si>
-  <si>
     <t>OK</t>
   </si>
   <si>
@@ -217,9 +202,6 @@
     <t>1. The operation is cancelled.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>1. The IA is not working</t>
   </si>
   <si>
@@ -232,13 +214,108 @@
     <t>BL</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>The button is not working</t>
-  </si>
-  <si>
-    <t>Blocked by PRO008</t>
+    <t>1. The user clicks products' home</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. The user fills the fields
+3. The user clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks in a product
+2. Modify the price</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The IA is not working
+https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link
+15/04/26: SOLUCIONADO: ProductsPage.tsx - se reemplazaron los alert() por un estado aiError con mensaje inline. Cuando el error es por falta de API key de OpenAI, se muestra 'La IA no está configurada. Ve a Configuración → Configuración de IA para añadir tu API key'.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Aparece un INTERNAL SERVER ERROR: PRO003.jpg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>No aparece la funcionalidad de "ES MENU" en el listado principal: PRO004.jpg</t>
+  </si>
+  <si>
+    <t>1. The user clicks icon next page (there are 20 products)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The button is not working
+https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
+15/04/26: Fixed: removed products?.meta.page and products?.meta.limit from useEffect deps. These caused the effect to re-run on page change and reset to page 1 via the debounced setTimeout. Now uses useRef to track current page for the auto-refresh interval.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The button is not working
+https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
+15/04/26: Fixed as part of PRO008: same root cause resolved.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The IA is not working
+https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link
+15/04/26: SOLUCIONADO: Mismo fix que PRO002. El feedback de error de IA ya no usa alert() sino un mensaje inline visible en el modal del producto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
   </si>
 </sst>
 </file>
@@ -266,15 +343,14 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -312,11 +388,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -333,18 +408,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
@@ -729,20 +806,22 @@
         <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H2" s="6"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -753,22 +832,22 @@
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -779,19 +858,17 @@
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>63</v>
+        <v>43</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -805,20 +882,20 @@
         <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>54</v>
+        <v>44</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -829,17 +906,17 @@
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -853,16 +930,16 @@
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -877,20 +954,20 @@
         <v>31</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -901,22 +978,20 @@
         <v>28</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -927,19 +1002,17 @@
         <v>29</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -953,14 +1026,14 @@
         <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="7" t="s">
-        <v>54</v>
+      <c r="G11" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H11" s="4"/>
     </row>
@@ -972,17 +1045,17 @@
         <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F12" s="3"/>
-      <c r="G12" s="7" t="s">
-        <v>54</v>
+      <c r="G12" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H12" s="4"/>
     </row>
@@ -994,17 +1067,17 @@
         <v>24</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="7" t="s">
-        <v>54</v>
+      <c r="G13" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H13" s="4"/>
     </row>
@@ -1013,22 +1086,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="H14" s="4"/>
     </row>
@@ -1037,25 +1110,27 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="4"/>
+      <c r="G15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="G2:G15">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
@@ -1071,8 +1146,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H9" r:id="rId1" xr:uid="{F1046E9F-9E81-47B2-8129-FD8B43AC3096}"/>
-    <hyperlink ref="H10" r:id="rId2" xr:uid="{237F15FD-C2AF-4DC2-8BF7-6C1C75C62567}"/>
+    <hyperlink ref="H9" r:id="rId1" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{F1046E9F-9E81-47B2-8129-FD8B43AC3096}"/>
+    <hyperlink ref="H10" r:id="rId2" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{D28FDDBA-F9DA-4502-A513-BA890D95754E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -411,7 +411,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">

--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621F1817-93A8-4769-8538-8C2629ECADD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACEA799-520C-4C1D-8862-C028B670B35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="74">
   <si>
     <t>Num</t>
   </si>
@@ -61,18 +61,6 @@
     <t>PTE</t>
   </si>
   <si>
-    <t>Create product</t>
-  </si>
-  <si>
-    <t>Modify product</t>
-  </si>
-  <si>
-    <t>Delete product</t>
-  </si>
-  <si>
-    <t>Products' home</t>
-  </si>
-  <si>
     <t>PRO005</t>
   </si>
   <si>
@@ -95,30 +83,6 @@
   </si>
   <si>
     <t>PRO012</t>
-  </si>
-  <si>
-    <t>Update price</t>
-  </si>
-  <si>
-    <t>Error without mandatory field</t>
-  </si>
-  <si>
-    <t>Error with an error in a field</t>
-  </si>
-  <si>
-    <t>Show next page</t>
-  </si>
-  <si>
-    <t>Shaw previous page</t>
-  </si>
-  <si>
-    <t>Filter: All categories, menus</t>
-  </si>
-  <si>
-    <t>Search a product</t>
-  </si>
-  <si>
-    <t>Cancel creation</t>
   </si>
   <si>
     <t>1. The user clicks icon pencil</t>
@@ -176,19 +140,10 @@
     <t>OK</t>
   </si>
   <si>
-    <t>1. The products' home is correctly</t>
-  </si>
-  <si>
     <t>PRO013</t>
   </si>
   <si>
     <t>PRO014</t>
-  </si>
-  <si>
-    <t>Cancel modification</t>
-  </si>
-  <si>
-    <t>Cancel deletion</t>
   </si>
   <si>
     <t>1. The user clicks "Nuevo producto" 
@@ -202,9 +157,6 @@
     <t>1. The operation is cancelled.</t>
   </si>
   <si>
-    <t>1. The IA is not working</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
@@ -212,14 +164,6 @@
   </si>
   <si>
     <t>BL</t>
-  </si>
-  <si>
-    <t>1. The user clicks products' home</t>
-  </si>
-  <si>
-    <t>1. The user clicks "Nuevo producto"
-2. The user fills the fields
-3. The user clicks "Crear"</t>
   </si>
   <si>
     <t>1. The user clicks in a product
@@ -316,6 +260,67 @@
   </si>
   <si>
     <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+  </si>
+  <si>
+    <t>Products home</t>
+  </si>
+  <si>
+    <t>1. The user clicks products home</t>
+  </si>
+  <si>
+    <t>1. The products home is correctly</t>
+  </si>
+  <si>
+    <t>Products: Modify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: Delete </t>
+  </si>
+  <si>
+    <t>Products: Delete, cancel</t>
+  </si>
+  <si>
+    <t>Products: Filter, All categories, menus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: Search </t>
+  </si>
+  <si>
+    <t>Products: Show next page</t>
+  </si>
+  <si>
+    <t>Products: Shaw previous page</t>
+  </si>
+  <si>
+    <t>Products: Cancel creation</t>
+  </si>
+  <si>
+    <t>Products: Modify ,cancel</t>
+  </si>
+  <si>
+    <t>1. The operation is canceled.</t>
+  </si>
+  <si>
+    <t>Products: Error without mandatory field</t>
+  </si>
+  <si>
+    <t>Products: Error with an error in a field</t>
+  </si>
+  <si>
+    <t>Products: Create, mandatory fields</t>
+  </si>
+  <si>
+    <t>Products: Create , all fields</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the mandatory fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the all fields
+3. Clicks "Crear"</t>
   </si>
 </sst>
 </file>
@@ -424,7 +429,38 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -759,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -803,22 +839,20 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>51</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -829,309 +863,335 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>59</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="6" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="6" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="G9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>70</v>
+        <v>12</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>34</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="G11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>72</v>
+      <c r="C16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G15">
+  <conditionalFormatting sqref="G2:G16">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -1146,8 +1206,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H9" r:id="rId1" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{F1046E9F-9E81-47B2-8129-FD8B43AC3096}"/>
-    <hyperlink ref="H10" r:id="rId2" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{D28FDDBA-F9DA-4502-A513-BA890D95754E}"/>
+    <hyperlink ref="H13" r:id="rId1" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{F1046E9F-9E81-47B2-8129-FD8B43AC3096}"/>
+    <hyperlink ref="H14" r:id="rId2" display="https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link" xr:uid="{D28FDDBA-F9DA-4502-A513-BA890D95754E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Productos.xlsx
+++ b/Web/TestCasesWeb/Productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACEA799-520C-4C1D-8862-C028B670B35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02060B0F-8610-4244-8331-6938845FE7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
   <si>
     <t>Num</t>
   </si>
@@ -168,6 +168,131 @@
   <si>
     <t>1. The user clicks in a product
 2. Modify the price</t>
+  </si>
+  <si>
+    <t>1. The user clicks icon next page (there are 20 products)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The button is not working
+https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
+15/04/26: Fixed: removed products?.meta.page and products?.meta.limit from useEffect deps. These caused the effect to re-run on page change and reset to page 1 via the debounced setTimeout. Now uses useRef to track current page for the auto-refresh interval.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The button is not working
+https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
+15/04/26: Fixed as part of PRO008: same root cause resolved.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The IA is not working
+https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link
+15/04/26: SOLUCIONADO: Mismo fix que PRO002. El feedback de error de IA ya no usa alert() sino un mensaje inline visible en el modal del producto.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+  </si>
+  <si>
+    <t>Products home</t>
+  </si>
+  <si>
+    <t>1. The user clicks products home</t>
+  </si>
+  <si>
+    <t>1. The products home is correctly</t>
+  </si>
+  <si>
+    <t>Products: Modify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: Delete </t>
+  </si>
+  <si>
+    <t>Products: Delete, cancel</t>
+  </si>
+  <si>
+    <t>Products: Filter, All categories, menus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products: Search </t>
+  </si>
+  <si>
+    <t>Products: Show next page</t>
+  </si>
+  <si>
+    <t>Products: Shaw previous page</t>
+  </si>
+  <si>
+    <t>Products: Cancel creation</t>
+  </si>
+  <si>
+    <t>Products: Modify ,cancel</t>
+  </si>
+  <si>
+    <t>1. The operation is canceled.</t>
+  </si>
+  <si>
+    <t>Products: Error without mandatory field</t>
+  </si>
+  <si>
+    <t>Products: Error with an error in a field</t>
+  </si>
+  <si>
+    <t>Products: Create, mandatory fields</t>
+  </si>
+  <si>
+    <t>Products: Create , all fields</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the mandatory fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Nuevo producto"
+2. Fills the all fields
+3. Clicks "Crear"</t>
+  </si>
+  <si>
+    <t>No aparece la funcionalidad de "ES MENU" en el listado principal: PRO004.jpg
+19/05/26: Aparecen menús entre los productos: PRO009.jpg</t>
   </si>
   <si>
     <r>
@@ -197,18 +322,33 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>No aparece la funcionalidad de "ES MENU" en el listado principal: PRO004.jpg</t>
-  </si>
-  <si>
-    <t>1. The user clicks icon next page (there are 20 products)</t>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">The button is not working
-https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
-15/04/26: Fixed: removed products?.meta.page and products?.meta.limit from useEffect deps. These caused the effect to re-run on page change and reset to page 1 via the debounced setTimeout. Now uses useRef to track current page for the auto-refresh interval.
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19/05/26: Da un fogonazo con el error, pero no se muestra. Tampoco se crea el producto.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. The IA is not working
+https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link
+15/04/26: SOLUCIONADO: ProductsPage.tsx - se reemplazaron los alert() por un estado aiError con mensaje inline. Cuando el error es por falta de API key de OpenAI, se muestra 'La IA no está configurada. Ve a Configuración → Configuración de IA para añadir tu API key'.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -219,115 +359,16 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
+      <t>17/04/26: Aparece un INTERNAL SERVER ERROR: PRO003.jpg
+19/05/26: Da un fogonazo con el error, pero no se muestra. Tampoco se crea el producto.</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The button is not working
-https://drive.google.com/file/d/1NEVph-7690Gw4j16HQBRHo9CDe9CLUbT/view?usp=drive_link
-15/04/26: Fixed as part of PRO008: same root cause resolved.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. The IA is not working
-https://drive.google.com/file/d/1sJVvwxAjHen83ICnAAqa12qjxpVXmmTu/view?usp=drive_link
-15/04/26: SOLUCIONADO: Mismo fix que PRO002. El feedback de error de IA ya no usa alert() sino un mensaje inline visible en el modal del producto.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
-    </r>
-  </si>
-  <si>
-    <t>17/04/26: Bloqueada por no poder crear productos:  PRO003.jpg</t>
-  </si>
-  <si>
-    <t>Products home</t>
-  </si>
-  <si>
-    <t>1. The user clicks products home</t>
-  </si>
-  <si>
-    <t>1. The products home is correctly</t>
-  </si>
-  <si>
-    <t>Products: Modify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products: Delete </t>
-  </si>
-  <si>
-    <t>Products: Delete, cancel</t>
-  </si>
-  <si>
-    <t>Products: Filter, All categories, menus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products: Search </t>
-  </si>
-  <si>
-    <t>Products: Show next page</t>
-  </si>
-  <si>
-    <t>Products: Shaw previous page</t>
-  </si>
-  <si>
-    <t>Products: Cancel creation</t>
-  </si>
-  <si>
-    <t>Products: Modify ,cancel</t>
-  </si>
-  <si>
-    <t>1. The operation is canceled.</t>
-  </si>
-  <si>
-    <t>Products: Error without mandatory field</t>
-  </si>
-  <si>
-    <t>Products: Error with an error in a field</t>
-  </si>
-  <si>
-    <t>Products: Create, mandatory fields</t>
-  </si>
-  <si>
-    <t>Products: Create , all fields</t>
-  </si>
-  <si>
-    <t>1. The user clicks "Nuevo producto"
-2. Fills the mandatory fields
-3. Clicks "Crear"</t>
-  </si>
-  <si>
-    <t>1. The user clicks "Nuevo producto"
-2. Fills the all fields
-3. Clicks "Crear"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -356,6 +397,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -429,38 +478,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -831,7 +849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -839,20 +857,20 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -863,10 +881,10 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>30</v>
@@ -876,7 +894,7 @@
         <v>44</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -887,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>30</v>
@@ -900,7 +918,7 @@
         <v>44</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -911,7 +929,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>41</v>
@@ -933,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>21</v>
@@ -946,7 +964,7 @@
         <v>46</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -957,16 +975,16 @@
         <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>38</v>
@@ -981,7 +999,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
@@ -1005,7 +1023,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -1029,7 +1047,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>47</v>
@@ -1053,7 +1071,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>23</v>
@@ -1077,7 +1095,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
@@ -1101,10 +1119,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>36</v>
@@ -1114,7 +1132,7 @@
         <v>46</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1125,7 +1143,7 @@
         <v>17</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
@@ -1138,7 +1156,7 @@
         <v>46</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1149,7 +1167,7 @@
         <v>39</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>27</v>
@@ -1173,7 +1191,7 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>28</v>
@@ -1186,7 +1204,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
